--- a/sample_attendance.xlsx
+++ b/sample_attendance.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2453" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2454" uniqueCount="87">
   <si>
     <t>Register Number</t>
   </si>
@@ -280,6 +280,9 @@
   </si>
   <si>
     <t>Kaviyadharshini S</t>
+  </si>
+  <si>
+    <t>613524104047</t>
   </si>
 </sst>
 </file>
@@ -1152,10 +1155,10 @@
         <v>73</v>
       </c>
       <c r="I2">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J2">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
@@ -1184,10 +1187,10 @@
         <v>15</v>
       </c>
       <c r="I3">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J3">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
@@ -1216,10 +1219,10 @@
         <v>77</v>
       </c>
       <c r="I4">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="J4">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
@@ -1248,10 +1251,10 @@
         <v>83</v>
       </c>
       <c r="I5">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J5">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
@@ -1280,10 +1283,10 @@
         <v>75</v>
       </c>
       <c r="I6">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J6">
-        <v>17</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
@@ -1312,10 +1315,10 @@
         <v>81</v>
       </c>
       <c r="I7">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J7">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
@@ -1344,10 +1347,10 @@
         <v>79</v>
       </c>
       <c r="I8">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J8">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
@@ -1376,10 +1379,10 @@
         <v>73</v>
       </c>
       <c r="I9">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J9">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
@@ -1408,10 +1411,10 @@
         <v>15</v>
       </c>
       <c r="I10">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J10">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
@@ -1440,10 +1443,10 @@
         <v>77</v>
       </c>
       <c r="I11">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="J11">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
@@ -1472,10 +1475,10 @@
         <v>83</v>
       </c>
       <c r="I12">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J12">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
@@ -1504,10 +1507,10 @@
         <v>75</v>
       </c>
       <c r="I13">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J13">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
@@ -1536,10 +1539,10 @@
         <v>81</v>
       </c>
       <c r="I14">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J14">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
@@ -1568,10 +1571,10 @@
         <v>79</v>
       </c>
       <c r="I15">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J15">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
@@ -1600,10 +1603,10 @@
         <v>73</v>
       </c>
       <c r="I16">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J16">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
@@ -1632,10 +1635,10 @@
         <v>15</v>
       </c>
       <c r="I17">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J17">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
@@ -1664,10 +1667,10 @@
         <v>77</v>
       </c>
       <c r="I18">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="J18">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
@@ -1696,10 +1699,10 @@
         <v>83</v>
       </c>
       <c r="I19">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J19">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
@@ -1728,10 +1731,10 @@
         <v>75</v>
       </c>
       <c r="I20">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J20">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
@@ -1760,10 +1763,10 @@
         <v>81</v>
       </c>
       <c r="I21">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J21">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
@@ -1792,10 +1795,10 @@
         <v>79</v>
       </c>
       <c r="I22">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J22">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
@@ -1824,10 +1827,10 @@
         <v>73</v>
       </c>
       <c r="I23">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J23">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
@@ -1856,10 +1859,10 @@
         <v>15</v>
       </c>
       <c r="I24">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J24">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
@@ -1888,10 +1891,10 @@
         <v>77</v>
       </c>
       <c r="I25">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="J25">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
@@ -1920,10 +1923,10 @@
         <v>83</v>
       </c>
       <c r="I26">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J26">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
@@ -1952,10 +1955,10 @@
         <v>75</v>
       </c>
       <c r="I27">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J27">
-        <v>17</v>
+        <v>26</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
@@ -1984,10 +1987,10 @@
         <v>81</v>
       </c>
       <c r="I28">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J28">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
@@ -2016,10 +2019,10 @@
         <v>79</v>
       </c>
       <c r="I29">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J29">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
@@ -2048,10 +2051,10 @@
         <v>73</v>
       </c>
       <c r="I30">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J30">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
@@ -2080,10 +2083,10 @@
         <v>15</v>
       </c>
       <c r="I31">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J31">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
@@ -2112,10 +2115,10 @@
         <v>77</v>
       </c>
       <c r="I32">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="J32">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
@@ -2144,10 +2147,10 @@
         <v>83</v>
       </c>
       <c r="I33">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J33">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
@@ -2176,10 +2179,10 @@
         <v>75</v>
       </c>
       <c r="I34">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J34">
-        <v>16</v>
+        <v>25</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">
@@ -2208,10 +2211,10 @@
         <v>81</v>
       </c>
       <c r="I35">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J35">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
@@ -2240,10 +2243,10 @@
         <v>79</v>
       </c>
       <c r="I36">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J36">
-        <v>11</v>
+        <v>19</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
@@ -2272,10 +2275,10 @@
         <v>73</v>
       </c>
       <c r="I37">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J37">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
@@ -2304,10 +2307,10 @@
         <v>15</v>
       </c>
       <c r="I38">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J38">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.3">
@@ -2336,10 +2339,10 @@
         <v>77</v>
       </c>
       <c r="I39">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="J39">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">
@@ -2368,10 +2371,10 @@
         <v>83</v>
       </c>
       <c r="I40">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J40">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.3">
@@ -2400,10 +2403,10 @@
         <v>75</v>
       </c>
       <c r="I41">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J41">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.3">
@@ -2432,10 +2435,10 @@
         <v>81</v>
       </c>
       <c r="I42">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J42">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.3">
@@ -2464,10 +2467,10 @@
         <v>79</v>
       </c>
       <c r="I43">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J43">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.3">
@@ -2496,10 +2499,10 @@
         <v>73</v>
       </c>
       <c r="I44">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J44">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.3">
@@ -2528,10 +2531,10 @@
         <v>15</v>
       </c>
       <c r="I45">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J45">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.3">
@@ -2560,10 +2563,10 @@
         <v>77</v>
       </c>
       <c r="I46">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="J46">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.3">
@@ -2592,10 +2595,10 @@
         <v>83</v>
       </c>
       <c r="I47">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J47">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.3">
@@ -2624,10 +2627,10 @@
         <v>75</v>
       </c>
       <c r="I48">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J48">
-        <v>17</v>
+        <v>26</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.3">
@@ -2656,10 +2659,10 @@
         <v>81</v>
       </c>
       <c r="I49">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J49">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.3">
@@ -2688,10 +2691,10 @@
         <v>79</v>
       </c>
       <c r="I50">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J50">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.3">
@@ -2720,10 +2723,10 @@
         <v>73</v>
       </c>
       <c r="I51">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J51">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.3">
@@ -2752,10 +2755,10 @@
         <v>15</v>
       </c>
       <c r="I52">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J52">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.3">
@@ -2784,10 +2787,10 @@
         <v>77</v>
       </c>
       <c r="I53">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="J53">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.3">
@@ -2816,10 +2819,10 @@
         <v>83</v>
       </c>
       <c r="I54">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J54">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.3">
@@ -2848,10 +2851,10 @@
         <v>75</v>
       </c>
       <c r="I55">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J55">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.3">
@@ -2880,10 +2883,10 @@
         <v>81</v>
       </c>
       <c r="I56">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J56">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.3">
@@ -2912,10 +2915,10 @@
         <v>79</v>
       </c>
       <c r="I57">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J57">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.3">
@@ -2944,10 +2947,10 @@
         <v>73</v>
       </c>
       <c r="I58">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J58">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.3">
@@ -2976,10 +2979,10 @@
         <v>15</v>
       </c>
       <c r="I59">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J59">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.3">
@@ -3008,10 +3011,10 @@
         <v>77</v>
       </c>
       <c r="I60">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="J60">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.3">
@@ -3040,10 +3043,10 @@
         <v>83</v>
       </c>
       <c r="I61">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J61">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.3">
@@ -3072,10 +3075,10 @@
         <v>75</v>
       </c>
       <c r="I62">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J62">
-        <v>11</v>
+        <v>19</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.3">
@@ -3104,10 +3107,10 @@
         <v>81</v>
       </c>
       <c r="I63">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J63">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.3">
@@ -3136,10 +3139,10 @@
         <v>79</v>
       </c>
       <c r="I64">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J64">
-        <v>11</v>
+        <v>18</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.3">
@@ -3168,10 +3171,10 @@
         <v>73</v>
       </c>
       <c r="I65">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J65">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.3">
@@ -3200,10 +3203,10 @@
         <v>15</v>
       </c>
       <c r="I66">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J66">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.3">
@@ -3232,10 +3235,10 @@
         <v>77</v>
       </c>
       <c r="I67">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="J67">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.3">
@@ -3264,10 +3267,10 @@
         <v>83</v>
       </c>
       <c r="I68">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J68">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.3">
@@ -3296,10 +3299,10 @@
         <v>75</v>
       </c>
       <c r="I69">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J69">
-        <v>16</v>
+        <v>25</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.3">
@@ -3328,10 +3331,10 @@
         <v>81</v>
       </c>
       <c r="I70">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J70">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.3">
@@ -3360,10 +3363,10 @@
         <v>79</v>
       </c>
       <c r="I71">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J71">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.3">
@@ -3392,10 +3395,10 @@
         <v>73</v>
       </c>
       <c r="I72">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J72">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.3">
@@ -3424,10 +3427,10 @@
         <v>15</v>
       </c>
       <c r="I73">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J73">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.3">
@@ -3456,10 +3459,10 @@
         <v>77</v>
       </c>
       <c r="I74">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="J74">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.3">
@@ -3488,10 +3491,10 @@
         <v>83</v>
       </c>
       <c r="I75">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J75">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.3">
@@ -3520,10 +3523,10 @@
         <v>75</v>
       </c>
       <c r="I76">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J76">
-        <v>17</v>
+        <v>26</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.3">
@@ -3552,10 +3555,10 @@
         <v>81</v>
       </c>
       <c r="I77">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J77">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.3">
@@ -3584,10 +3587,10 @@
         <v>79</v>
       </c>
       <c r="I78">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J78">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.3">
@@ -3616,10 +3619,10 @@
         <v>73</v>
       </c>
       <c r="I79">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J79">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.3">
@@ -3648,10 +3651,10 @@
         <v>15</v>
       </c>
       <c r="I80">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J80">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.3">
@@ -3680,10 +3683,10 @@
         <v>77</v>
       </c>
       <c r="I81">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="J81">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.3">
@@ -3712,10 +3715,10 @@
         <v>83</v>
       </c>
       <c r="I82">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J82">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.3">
@@ -3744,10 +3747,10 @@
         <v>75</v>
       </c>
       <c r="I83">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J83">
-        <v>16</v>
+        <v>25</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.3">
@@ -3776,10 +3779,10 @@
         <v>81</v>
       </c>
       <c r="I84">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J84">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.3">
@@ -3808,10 +3811,10 @@
         <v>79</v>
       </c>
       <c r="I85">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J85">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.3">
@@ -3840,10 +3843,10 @@
         <v>73</v>
       </c>
       <c r="I86">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J86">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.3">
@@ -3872,10 +3875,10 @@
         <v>15</v>
       </c>
       <c r="I87">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J87">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.3">
@@ -3904,10 +3907,10 @@
         <v>77</v>
       </c>
       <c r="I88">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="J88">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.3">
@@ -3936,10 +3939,10 @@
         <v>83</v>
       </c>
       <c r="I89">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J89">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.3">
@@ -3968,10 +3971,10 @@
         <v>75</v>
       </c>
       <c r="I90">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J90">
-        <v>12</v>
+        <v>21</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.3">
@@ -4000,10 +4003,10 @@
         <v>81</v>
       </c>
       <c r="I91">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J91">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.3">
@@ -4032,10 +4035,10 @@
         <v>79</v>
       </c>
       <c r="I92">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J92">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.3">
@@ -4064,7 +4067,7 @@
         <v>73</v>
       </c>
       <c r="I93">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J93">
         <v>8</v>
@@ -4096,10 +4099,10 @@
         <v>15</v>
       </c>
       <c r="I94">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J94">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.3">
@@ -4128,10 +4131,10 @@
         <v>77</v>
       </c>
       <c r="I95">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="J95">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.3">
@@ -4160,10 +4163,10 @@
         <v>83</v>
       </c>
       <c r="I96">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J96">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.3">
@@ -4192,10 +4195,10 @@
         <v>75</v>
       </c>
       <c r="I97">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J97">
-        <v>18</v>
+        <v>27</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.3">
@@ -4224,10 +4227,10 @@
         <v>81</v>
       </c>
       <c r="I98">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J98">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.3">
@@ -4256,10 +4259,10 @@
         <v>79</v>
       </c>
       <c r="I99">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J99">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.3">
@@ -4288,10 +4291,10 @@
         <v>73</v>
       </c>
       <c r="I100">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J100">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.3">
@@ -4320,10 +4323,10 @@
         <v>15</v>
       </c>
       <c r="I101">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J101">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.3">
@@ -4352,10 +4355,10 @@
         <v>77</v>
       </c>
       <c r="I102">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="J102">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.3">
@@ -4384,10 +4387,10 @@
         <v>83</v>
       </c>
       <c r="I103">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J103">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.3">
@@ -4416,10 +4419,10 @@
         <v>75</v>
       </c>
       <c r="I104">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J104">
-        <v>16</v>
+        <v>25</v>
       </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.3">
@@ -4448,10 +4451,10 @@
         <v>81</v>
       </c>
       <c r="I105">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J105">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.3">
@@ -4480,10 +4483,10 @@
         <v>79</v>
       </c>
       <c r="I106">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J106">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.3">
@@ -4512,10 +4515,10 @@
         <v>73</v>
       </c>
       <c r="I107">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J107">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.3">
@@ -4544,10 +4547,10 @@
         <v>15</v>
       </c>
       <c r="I108">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J108">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.3">
@@ -4576,10 +4579,10 @@
         <v>77</v>
       </c>
       <c r="I109">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="J109">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.3">
@@ -4608,10 +4611,10 @@
         <v>83</v>
       </c>
       <c r="I110">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J110">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.3">
@@ -4640,10 +4643,10 @@
         <v>75</v>
       </c>
       <c r="I111">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J111">
-        <v>16</v>
+        <v>25</v>
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.3">
@@ -4672,10 +4675,10 @@
         <v>81</v>
       </c>
       <c r="I112">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J112">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.3">
@@ -4704,10 +4707,10 @@
         <v>79</v>
       </c>
       <c r="I113">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J113">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.3">
@@ -4736,10 +4739,10 @@
         <v>73</v>
       </c>
       <c r="I114">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J114">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.3">
@@ -4768,10 +4771,10 @@
         <v>15</v>
       </c>
       <c r="I115">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J115">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.3">
@@ -4800,10 +4803,10 @@
         <v>77</v>
       </c>
       <c r="I116">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="J116">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.3">
@@ -4832,10 +4835,10 @@
         <v>83</v>
       </c>
       <c r="I117">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J117">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.3">
@@ -4864,10 +4867,10 @@
         <v>75</v>
       </c>
       <c r="I118">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J118">
-        <v>17</v>
+        <v>26</v>
       </c>
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.3">
@@ -4896,10 +4899,10 @@
         <v>81</v>
       </c>
       <c r="I119">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J119">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.3">
@@ -4928,10 +4931,10 @@
         <v>79</v>
       </c>
       <c r="I120">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J120">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.3">
@@ -4960,10 +4963,10 @@
         <v>73</v>
       </c>
       <c r="I121">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J121">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.3">
@@ -4992,10 +4995,10 @@
         <v>15</v>
       </c>
       <c r="I122">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J122">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.3">
@@ -5024,10 +5027,10 @@
         <v>77</v>
       </c>
       <c r="I123">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="J123">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.3">
@@ -5056,10 +5059,10 @@
         <v>83</v>
       </c>
       <c r="I124">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J124">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.3">
@@ -5088,10 +5091,10 @@
         <v>75</v>
       </c>
       <c r="I125">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J125">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.3">
@@ -5120,10 +5123,10 @@
         <v>81</v>
       </c>
       <c r="I126">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J126">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.3">
@@ -5152,10 +5155,10 @@
         <v>79</v>
       </c>
       <c r="I127">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J127">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.3">
@@ -5184,10 +5187,10 @@
         <v>73</v>
       </c>
       <c r="I128">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J128">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.3">
@@ -5216,10 +5219,10 @@
         <v>15</v>
       </c>
       <c r="I129">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J129">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.3">
@@ -5248,10 +5251,10 @@
         <v>77</v>
       </c>
       <c r="I130">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="J130">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.3">
@@ -5280,10 +5283,10 @@
         <v>83</v>
       </c>
       <c r="I131">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J131">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.3">
@@ -5312,10 +5315,10 @@
         <v>75</v>
       </c>
       <c r="I132">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J132">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.3">
@@ -5344,10 +5347,10 @@
         <v>81</v>
       </c>
       <c r="I133">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J133">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.3">
@@ -5376,10 +5379,10 @@
         <v>79</v>
       </c>
       <c r="I134">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J134">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.3">
@@ -5408,10 +5411,10 @@
         <v>73</v>
       </c>
       <c r="I135">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J135">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.3">
@@ -5440,10 +5443,10 @@
         <v>15</v>
       </c>
       <c r="I136">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J136">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.3">
@@ -5472,10 +5475,10 @@
         <v>77</v>
       </c>
       <c r="I137">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="J137">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.3">
@@ -5504,10 +5507,10 @@
         <v>83</v>
       </c>
       <c r="I138">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J138">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.3">
@@ -5536,10 +5539,10 @@
         <v>75</v>
       </c>
       <c r="I139">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J139">
-        <v>18</v>
+        <v>27</v>
       </c>
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.3">
@@ -5568,10 +5571,10 @@
         <v>81</v>
       </c>
       <c r="I140">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J140">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.3">
@@ -5600,10 +5603,10 @@
         <v>79</v>
       </c>
       <c r="I141">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J141">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.3">
@@ -5632,10 +5635,10 @@
         <v>73</v>
       </c>
       <c r="I142">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J142">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.3">
@@ -5664,10 +5667,10 @@
         <v>15</v>
       </c>
       <c r="I143">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J143">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.3">
@@ -5696,10 +5699,10 @@
         <v>77</v>
       </c>
       <c r="I144">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="J144">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.3">
@@ -5728,10 +5731,10 @@
         <v>83</v>
       </c>
       <c r="I145">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J145">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.3">
@@ -5760,10 +5763,10 @@
         <v>75</v>
       </c>
       <c r="I146">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J146">
-        <v>17</v>
+        <v>26</v>
       </c>
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.3">
@@ -5792,10 +5795,10 @@
         <v>81</v>
       </c>
       <c r="I147">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J147">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.3">
@@ -5824,10 +5827,10 @@
         <v>79</v>
       </c>
       <c r="I148">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J148">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.3">
@@ -5856,10 +5859,10 @@
         <v>73</v>
       </c>
       <c r="I149">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J149">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.3">
@@ -5888,10 +5891,10 @@
         <v>15</v>
       </c>
       <c r="I150">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J150">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.3">
@@ -5920,10 +5923,10 @@
         <v>77</v>
       </c>
       <c r="I151">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="J151">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="152" spans="1:10" x14ac:dyDescent="0.3">
@@ -5952,10 +5955,10 @@
         <v>83</v>
       </c>
       <c r="I152">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J152">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="153" spans="1:10" x14ac:dyDescent="0.3">
@@ -5984,10 +5987,10 @@
         <v>75</v>
       </c>
       <c r="I153">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J153">
-        <v>17</v>
+        <v>26</v>
       </c>
     </row>
     <row r="154" spans="1:10" x14ac:dyDescent="0.3">
@@ -6016,10 +6019,10 @@
         <v>81</v>
       </c>
       <c r="I154">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J154">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="155" spans="1:10" x14ac:dyDescent="0.3">
@@ -6048,10 +6051,10 @@
         <v>79</v>
       </c>
       <c r="I155">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J155">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="156" spans="1:10" x14ac:dyDescent="0.3">
@@ -6080,10 +6083,10 @@
         <v>73</v>
       </c>
       <c r="I156">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J156">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="157" spans="1:10" x14ac:dyDescent="0.3">
@@ -6112,10 +6115,10 @@
         <v>15</v>
       </c>
       <c r="I157">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J157">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="158" spans="1:10" x14ac:dyDescent="0.3">
@@ -6144,10 +6147,10 @@
         <v>77</v>
       </c>
       <c r="I158">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="J158">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="159" spans="1:10" x14ac:dyDescent="0.3">
@@ -6176,10 +6179,10 @@
         <v>83</v>
       </c>
       <c r="I159">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J159">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="160" spans="1:10" x14ac:dyDescent="0.3">
@@ -6208,10 +6211,10 @@
         <v>75</v>
       </c>
       <c r="I160">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J160">
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="161" spans="1:10" x14ac:dyDescent="0.3">
@@ -6240,10 +6243,10 @@
         <v>81</v>
       </c>
       <c r="I161">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J161">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.3">
@@ -6272,10 +6275,10 @@
         <v>79</v>
       </c>
       <c r="I162">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J162">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.3">
@@ -6304,10 +6307,10 @@
         <v>73</v>
       </c>
       <c r="I163">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J163">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.3">
@@ -6336,10 +6339,10 @@
         <v>15</v>
       </c>
       <c r="I164">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J164">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.3">
@@ -6368,10 +6371,10 @@
         <v>77</v>
       </c>
       <c r="I165">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="J165">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="166" spans="1:10" x14ac:dyDescent="0.3">
@@ -6400,10 +6403,10 @@
         <v>83</v>
       </c>
       <c r="I166">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J166">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="167" spans="1:10" x14ac:dyDescent="0.3">
@@ -6432,10 +6435,10 @@
         <v>75</v>
       </c>
       <c r="I167">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J167">
-        <v>17</v>
+        <v>26</v>
       </c>
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.3">
@@ -6464,10 +6467,10 @@
         <v>81</v>
       </c>
       <c r="I168">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J168">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="169" spans="1:10" x14ac:dyDescent="0.3">
@@ -6496,10 +6499,10 @@
         <v>79</v>
       </c>
       <c r="I169">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J169">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="170" spans="1:10" x14ac:dyDescent="0.3">
@@ -6528,10 +6531,10 @@
         <v>73</v>
       </c>
       <c r="I170">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J170">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="171" spans="1:10" x14ac:dyDescent="0.3">
@@ -6560,10 +6563,10 @@
         <v>15</v>
       </c>
       <c r="I171">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J171">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="172" spans="1:10" x14ac:dyDescent="0.3">
@@ -6592,10 +6595,10 @@
         <v>77</v>
       </c>
       <c r="I172">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="J172">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="173" spans="1:10" x14ac:dyDescent="0.3">
@@ -6624,10 +6627,10 @@
         <v>83</v>
       </c>
       <c r="I173">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J173">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.3">
@@ -6656,10 +6659,10 @@
         <v>75</v>
       </c>
       <c r="I174">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J174">
-        <v>17</v>
+        <v>26</v>
       </c>
     </row>
     <row r="175" spans="1:10" x14ac:dyDescent="0.3">
@@ -6688,10 +6691,10 @@
         <v>81</v>
       </c>
       <c r="I175">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J175">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="176" spans="1:10" x14ac:dyDescent="0.3">
@@ -6720,10 +6723,10 @@
         <v>79</v>
       </c>
       <c r="I176">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J176">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="177" spans="1:10" x14ac:dyDescent="0.3">
@@ -6752,10 +6755,10 @@
         <v>73</v>
       </c>
       <c r="I177">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J177">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="178" spans="1:10" x14ac:dyDescent="0.3">
@@ -6784,10 +6787,10 @@
         <v>15</v>
       </c>
       <c r="I178">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J178">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="179" spans="1:10" x14ac:dyDescent="0.3">
@@ -6816,10 +6819,10 @@
         <v>77</v>
       </c>
       <c r="I179">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="J179">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="180" spans="1:10" x14ac:dyDescent="0.3">
@@ -6848,10 +6851,10 @@
         <v>83</v>
       </c>
       <c r="I180">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J180">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="181" spans="1:10" x14ac:dyDescent="0.3">
@@ -6880,10 +6883,10 @@
         <v>75</v>
       </c>
       <c r="I181">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J181">
-        <v>17</v>
+        <v>26</v>
       </c>
     </row>
     <row r="182" spans="1:10" x14ac:dyDescent="0.3">
@@ -6912,10 +6915,10 @@
         <v>81</v>
       </c>
       <c r="I182">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J182">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="183" spans="1:10" x14ac:dyDescent="0.3">
@@ -6944,10 +6947,10 @@
         <v>79</v>
       </c>
       <c r="I183">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J183">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="184" spans="1:10" x14ac:dyDescent="0.3">
@@ -6976,10 +6979,10 @@
         <v>73</v>
       </c>
       <c r="I184">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J184">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="185" spans="1:10" x14ac:dyDescent="0.3">
@@ -7008,10 +7011,10 @@
         <v>15</v>
       </c>
       <c r="I185">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J185">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="186" spans="1:10" x14ac:dyDescent="0.3">
@@ -7040,10 +7043,10 @@
         <v>77</v>
       </c>
       <c r="I186">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="J186">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="187" spans="1:10" x14ac:dyDescent="0.3">
@@ -7072,10 +7075,10 @@
         <v>83</v>
       </c>
       <c r="I187">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J187">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="188" spans="1:10" x14ac:dyDescent="0.3">
@@ -7104,10 +7107,10 @@
         <v>75</v>
       </c>
       <c r="I188">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J188">
-        <v>17</v>
+        <v>26</v>
       </c>
     </row>
     <row r="189" spans="1:10" x14ac:dyDescent="0.3">
@@ -7136,10 +7139,10 @@
         <v>81</v>
       </c>
       <c r="I189">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J189">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="190" spans="1:10" x14ac:dyDescent="0.3">
@@ -7168,10 +7171,10 @@
         <v>79</v>
       </c>
       <c r="I190">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J190">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="191" spans="1:10" x14ac:dyDescent="0.3">
@@ -7200,7 +7203,7 @@
         <v>73</v>
       </c>
       <c r="I191">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J191">
         <v>7</v>
@@ -7232,10 +7235,10 @@
         <v>15</v>
       </c>
       <c r="I192">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J192">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="193" spans="1:10" x14ac:dyDescent="0.3">
@@ -7264,10 +7267,10 @@
         <v>77</v>
       </c>
       <c r="I193">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="J193">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="194" spans="1:10" x14ac:dyDescent="0.3">
@@ -7296,10 +7299,10 @@
         <v>83</v>
       </c>
       <c r="I194">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J194">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="195" spans="1:10" x14ac:dyDescent="0.3">
@@ -7328,10 +7331,10 @@
         <v>75</v>
       </c>
       <c r="I195">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J195">
-        <v>17</v>
+        <v>26</v>
       </c>
     </row>
     <row r="196" spans="1:10" x14ac:dyDescent="0.3">
@@ -7360,10 +7363,10 @@
         <v>81</v>
       </c>
       <c r="I196">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J196">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="197" spans="1:10" x14ac:dyDescent="0.3">
@@ -7392,18 +7395,18 @@
         <v>79</v>
       </c>
       <c r="I197">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J197">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="198" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A198" s="1" t="s">
-        <v>84</v>
+      <c r="A198" s="1">
+        <v>613524104038</v>
       </c>
       <c r="B198" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C198" t="s">
         <v>11</v>
@@ -7424,18 +7427,18 @@
         <v>73</v>
       </c>
       <c r="I198">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J198">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="199" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A199" s="1" t="s">
-        <v>84</v>
+      <c r="A199" s="1">
+        <v>613524104038</v>
       </c>
       <c r="B199" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C199" t="s">
         <v>11</v>
@@ -7456,18 +7459,18 @@
         <v>15</v>
       </c>
       <c r="I199">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J199">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="200" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A200" s="1" t="s">
-        <v>84</v>
+      <c r="A200" s="1">
+        <v>613524104038</v>
       </c>
       <c r="B200" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C200" t="s">
         <v>11</v>
@@ -7488,18 +7491,18 @@
         <v>77</v>
       </c>
       <c r="I200">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="J200">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="201" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A201" s="1" t="s">
-        <v>84</v>
+      <c r="A201" s="1">
+        <v>613524104038</v>
       </c>
       <c r="B201" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C201" t="s">
         <v>11</v>
@@ -7520,18 +7523,18 @@
         <v>83</v>
       </c>
       <c r="I201">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J201">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="202" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A202" s="1" t="s">
-        <v>84</v>
+      <c r="A202" s="1">
+        <v>613524104038</v>
       </c>
       <c r="B202" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C202" t="s">
         <v>11</v>
@@ -7552,18 +7555,18 @@
         <v>75</v>
       </c>
       <c r="I202">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J202">
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="203" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A203" s="1" t="s">
-        <v>84</v>
+      <c r="A203" s="1">
+        <v>613524104038</v>
       </c>
       <c r="B203" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C203" t="s">
         <v>11</v>
@@ -7584,18 +7587,18 @@
         <v>81</v>
       </c>
       <c r="I203">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J203">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="204" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A204" s="1" t="s">
-        <v>84</v>
+      <c r="A204" s="1">
+        <v>613524104038</v>
       </c>
       <c r="B204" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C204" t="s">
         <v>11</v>
@@ -7616,18 +7619,18 @@
         <v>79</v>
       </c>
       <c r="I204">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J204">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="205" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A205" s="1">
-        <v>613524104038</v>
+        <v>613524104039</v>
       </c>
       <c r="B205" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C205" t="s">
         <v>11</v>
@@ -7648,18 +7651,18 @@
         <v>73</v>
       </c>
       <c r="I205">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J205">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="206" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A206" s="1">
-        <v>613524104038</v>
+        <v>613524104039</v>
       </c>
       <c r="B206" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C206" t="s">
         <v>11</v>
@@ -7680,18 +7683,18 @@
         <v>15</v>
       </c>
       <c r="I206">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J206">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="207" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A207" s="1">
-        <v>613524104038</v>
+        <v>613524104039</v>
       </c>
       <c r="B207" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C207" t="s">
         <v>11</v>
@@ -7712,18 +7715,18 @@
         <v>77</v>
       </c>
       <c r="I207">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="J207">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="208" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A208" s="1">
-        <v>613524104038</v>
+        <v>613524104039</v>
       </c>
       <c r="B208" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C208" t="s">
         <v>11</v>
@@ -7744,18 +7747,18 @@
         <v>83</v>
       </c>
       <c r="I208">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J208">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="209" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A209" s="1">
-        <v>613524104038</v>
+        <v>613524104039</v>
       </c>
       <c r="B209" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C209" t="s">
         <v>11</v>
@@ -7776,18 +7779,18 @@
         <v>75</v>
       </c>
       <c r="I209">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J209">
-        <v>17</v>
+        <v>26</v>
       </c>
     </row>
     <row r="210" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A210" s="1">
-        <v>613524104038</v>
+        <v>613524104039</v>
       </c>
       <c r="B210" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C210" t="s">
         <v>11</v>
@@ -7808,18 +7811,18 @@
         <v>81</v>
       </c>
       <c r="I210">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J210">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="211" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A211" s="1">
-        <v>613524104038</v>
+        <v>613524104039</v>
       </c>
       <c r="B211" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C211" t="s">
         <v>11</v>
@@ -7840,18 +7843,18 @@
         <v>79</v>
       </c>
       <c r="I211">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J211">
-        <v>11</v>
+        <v>20</v>
       </c>
     </row>
     <row r="212" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A212" s="1">
-        <v>613524104039</v>
+        <v>613524104040</v>
       </c>
       <c r="B212" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C212" t="s">
         <v>11</v>
@@ -7872,18 +7875,18 @@
         <v>73</v>
       </c>
       <c r="I212">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J212">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="213" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A213" s="1">
-        <v>613524104039</v>
+        <v>613524104040</v>
       </c>
       <c r="B213" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C213" t="s">
         <v>11</v>
@@ -7904,18 +7907,18 @@
         <v>15</v>
       </c>
       <c r="I213">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J213">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="214" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A214" s="1">
-        <v>613524104039</v>
+        <v>613524104040</v>
       </c>
       <c r="B214" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C214" t="s">
         <v>11</v>
@@ -7936,18 +7939,18 @@
         <v>77</v>
       </c>
       <c r="I214">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="J214">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="215" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A215" s="1">
-        <v>613524104039</v>
+        <v>613524104040</v>
       </c>
       <c r="B215" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C215" t="s">
         <v>11</v>
@@ -7968,18 +7971,18 @@
         <v>83</v>
       </c>
       <c r="I215">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J215">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="216" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A216" s="1">
-        <v>613524104039</v>
+        <v>613524104040</v>
       </c>
       <c r="B216" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C216" t="s">
         <v>11</v>
@@ -8000,18 +8003,18 @@
         <v>75</v>
       </c>
       <c r="I216">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J216">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="217" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A217" s="1">
-        <v>613524104039</v>
+        <v>613524104040</v>
       </c>
       <c r="B217" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C217" t="s">
         <v>11</v>
@@ -8032,18 +8035,18 @@
         <v>81</v>
       </c>
       <c r="I217">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J217">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="218" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A218" s="1">
-        <v>613524104039</v>
+        <v>613524104040</v>
       </c>
       <c r="B218" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C218" t="s">
         <v>11</v>
@@ -8064,18 +8067,18 @@
         <v>79</v>
       </c>
       <c r="I218">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J218">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="219" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A219" s="1">
-        <v>613524104040</v>
+        <v>613524104041</v>
       </c>
       <c r="B219" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C219" t="s">
         <v>11</v>
@@ -8096,18 +8099,18 @@
         <v>73</v>
       </c>
       <c r="I219">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J219">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="220" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A220" s="1">
-        <v>613524104040</v>
+        <v>613524104041</v>
       </c>
       <c r="B220" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C220" t="s">
         <v>11</v>
@@ -8128,18 +8131,18 @@
         <v>15</v>
       </c>
       <c r="I220">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J220">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="221" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A221" s="1">
-        <v>613524104040</v>
+        <v>613524104041</v>
       </c>
       <c r="B221" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C221" t="s">
         <v>11</v>
@@ -8160,18 +8163,18 @@
         <v>77</v>
       </c>
       <c r="I221">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="J221">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="222" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A222" s="1">
-        <v>613524104040</v>
+        <v>613524104041</v>
       </c>
       <c r="B222" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C222" t="s">
         <v>11</v>
@@ -8192,18 +8195,18 @@
         <v>83</v>
       </c>
       <c r="I222">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J222">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="223" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A223" s="1">
-        <v>613524104040</v>
+        <v>613524104041</v>
       </c>
       <c r="B223" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C223" t="s">
         <v>11</v>
@@ -8224,18 +8227,18 @@
         <v>75</v>
       </c>
       <c r="I223">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J223">
-        <v>12</v>
+        <v>27</v>
       </c>
     </row>
     <row r="224" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A224" s="1">
-        <v>613524104040</v>
+        <v>613524104041</v>
       </c>
       <c r="B224" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C224" t="s">
         <v>11</v>
@@ -8256,18 +8259,18 @@
         <v>81</v>
       </c>
       <c r="I224">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J224">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="225" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A225" s="1">
-        <v>613524104040</v>
+        <v>613524104041</v>
       </c>
       <c r="B225" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C225" t="s">
         <v>11</v>
@@ -8288,18 +8291,18 @@
         <v>79</v>
       </c>
       <c r="I225">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J225">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="226" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A226" s="1">
-        <v>613524104041</v>
+        <v>613524104042</v>
       </c>
       <c r="B226" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C226" t="s">
         <v>11</v>
@@ -8320,18 +8323,18 @@
         <v>73</v>
       </c>
       <c r="I226">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J226">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="227" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A227" s="1">
-        <v>613524104041</v>
+        <v>613524104042</v>
       </c>
       <c r="B227" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C227" t="s">
         <v>11</v>
@@ -8352,18 +8355,18 @@
         <v>15</v>
       </c>
       <c r="I227">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J227">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="228" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A228" s="1">
-        <v>613524104041</v>
+        <v>613524104042</v>
       </c>
       <c r="B228" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C228" t="s">
         <v>11</v>
@@ -8384,18 +8387,18 @@
         <v>77</v>
       </c>
       <c r="I228">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="J228">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="229" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A229" s="1">
-        <v>613524104041</v>
+        <v>613524104042</v>
       </c>
       <c r="B229" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C229" t="s">
         <v>11</v>
@@ -8416,18 +8419,18 @@
         <v>83</v>
       </c>
       <c r="I229">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J229">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="230" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A230" s="1">
-        <v>613524104041</v>
+        <v>613524104042</v>
       </c>
       <c r="B230" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C230" t="s">
         <v>11</v>
@@ -8448,18 +8451,18 @@
         <v>75</v>
       </c>
       <c r="I230">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J230">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="231" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A231" s="1">
-        <v>613524104041</v>
+        <v>613524104042</v>
       </c>
       <c r="B231" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C231" t="s">
         <v>11</v>
@@ -8480,18 +8483,18 @@
         <v>81</v>
       </c>
       <c r="I231">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J231">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="232" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A232" s="1">
-        <v>613524104041</v>
+        <v>613524104042</v>
       </c>
       <c r="B232" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C232" t="s">
         <v>11</v>
@@ -8512,18 +8515,18 @@
         <v>79</v>
       </c>
       <c r="I232">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J232">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="233" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A233" s="1">
-        <v>613524104042</v>
+        <v>613524104044</v>
       </c>
       <c r="B233" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C233" t="s">
         <v>11</v>
@@ -8544,18 +8547,18 @@
         <v>73</v>
       </c>
       <c r="I233">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J233">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="234" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A234" s="1">
-        <v>613524104042</v>
+        <v>613524104044</v>
       </c>
       <c r="B234" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C234" t="s">
         <v>11</v>
@@ -8576,18 +8579,18 @@
         <v>15</v>
       </c>
       <c r="I234">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J234">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="235" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A235" s="1">
-        <v>613524104042</v>
+        <v>613524104044</v>
       </c>
       <c r="B235" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C235" t="s">
         <v>11</v>
@@ -8608,18 +8611,18 @@
         <v>77</v>
       </c>
       <c r="I235">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="J235">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="236" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A236" s="1">
-        <v>613524104042</v>
+        <v>613524104044</v>
       </c>
       <c r="B236" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C236" t="s">
         <v>11</v>
@@ -8640,18 +8643,18 @@
         <v>83</v>
       </c>
       <c r="I236">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J236">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="237" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A237" s="1">
-        <v>613524104042</v>
+        <v>613524104044</v>
       </c>
       <c r="B237" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C237" t="s">
         <v>11</v>
@@ -8672,18 +8675,18 @@
         <v>75</v>
       </c>
       <c r="I237">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J237">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="238" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A238" s="1">
-        <v>613524104042</v>
+        <v>613524104044</v>
       </c>
       <c r="B238" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C238" t="s">
         <v>11</v>
@@ -8704,18 +8707,18 @@
         <v>81</v>
       </c>
       <c r="I238">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J238">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="239" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A239" s="1">
-        <v>613524104042</v>
+        <v>613524104044</v>
       </c>
       <c r="B239" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C239" t="s">
         <v>11</v>
@@ -8736,18 +8739,18 @@
         <v>79</v>
       </c>
       <c r="I239">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J239">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="240" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A240" s="1">
-        <v>613524104044</v>
+        <v>613524104045</v>
       </c>
       <c r="B240" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C240" t="s">
         <v>11</v>
@@ -8768,18 +8771,18 @@
         <v>73</v>
       </c>
       <c r="I240">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J240">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="241" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A241" s="1">
-        <v>613524104044</v>
+        <v>613524104045</v>
       </c>
       <c r="B241" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C241" t="s">
         <v>11</v>
@@ -8800,18 +8803,18 @@
         <v>15</v>
       </c>
       <c r="I241">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J241">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="242" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A242" s="1">
-        <v>613524104044</v>
+        <v>613524104045</v>
       </c>
       <c r="B242" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C242" t="s">
         <v>11</v>
@@ -8832,18 +8835,18 @@
         <v>77</v>
       </c>
       <c r="I242">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="J242">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="243" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A243" s="1">
-        <v>613524104044</v>
+        <v>613524104045</v>
       </c>
       <c r="B243" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C243" t="s">
         <v>11</v>
@@ -8864,18 +8867,18 @@
         <v>83</v>
       </c>
       <c r="I243">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J243">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="244" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A244" s="1">
-        <v>613524104044</v>
+        <v>613524104045</v>
       </c>
       <c r="B244" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C244" t="s">
         <v>11</v>
@@ -8896,18 +8899,18 @@
         <v>75</v>
       </c>
       <c r="I244">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J244">
-        <v>16</v>
+        <v>25</v>
       </c>
     </row>
     <row r="245" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A245" s="1">
-        <v>613524104044</v>
+        <v>613524104045</v>
       </c>
       <c r="B245" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C245" t="s">
         <v>11</v>
@@ -8928,18 +8931,18 @@
         <v>81</v>
       </c>
       <c r="I245">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J245">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="246" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A246" s="1">
-        <v>613524104044</v>
+        <v>613524104045</v>
       </c>
       <c r="B246" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C246" t="s">
         <v>11</v>
@@ -8960,18 +8963,18 @@
         <v>79</v>
       </c>
       <c r="I246">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J246">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="247" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A247" s="1">
-        <v>613524104045</v>
+        <v>613524104046</v>
       </c>
       <c r="B247" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C247" t="s">
         <v>11</v>
@@ -8992,18 +8995,18 @@
         <v>73</v>
       </c>
       <c r="I247">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J247">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="248" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A248" s="1">
-        <v>613524104045</v>
+        <v>613524104046</v>
       </c>
       <c r="B248" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C248" t="s">
         <v>11</v>
@@ -9024,18 +9027,18 @@
         <v>15</v>
       </c>
       <c r="I248">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J248">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="249" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A249" s="1">
-        <v>613524104045</v>
+        <v>613524104046</v>
       </c>
       <c r="B249" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C249" t="s">
         <v>11</v>
@@ -9056,18 +9059,18 @@
         <v>77</v>
       </c>
       <c r="I249">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="J249">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="250" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A250" s="1">
-        <v>613524104045</v>
+        <v>613524104046</v>
       </c>
       <c r="B250" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C250" t="s">
         <v>11</v>
@@ -9088,18 +9091,18 @@
         <v>83</v>
       </c>
       <c r="I250">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J250">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="251" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A251" s="1">
-        <v>613524104045</v>
+        <v>613524104046</v>
       </c>
       <c r="B251" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C251" t="s">
         <v>11</v>
@@ -9120,18 +9123,18 @@
         <v>75</v>
       </c>
       <c r="I251">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J251">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="252" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A252" s="1">
-        <v>613524104045</v>
+        <v>613524104046</v>
       </c>
       <c r="B252" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C252" t="s">
         <v>11</v>
@@ -9152,18 +9155,18 @@
         <v>81</v>
       </c>
       <c r="I252">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J252">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="253" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A253" s="1">
-        <v>613524104045</v>
+        <v>613524104046</v>
       </c>
       <c r="B253" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C253" t="s">
         <v>11</v>
@@ -9184,18 +9187,18 @@
         <v>79</v>
       </c>
       <c r="I253">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J253">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="254" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A254" s="1">
-        <v>613524104046</v>
+        <v>613524104047</v>
       </c>
       <c r="B254" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C254" t="s">
         <v>11</v>
@@ -9216,18 +9219,18 @@
         <v>73</v>
       </c>
       <c r="I254">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J254">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="255" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A255" s="1">
-        <v>613524104046</v>
+        <v>613524104047</v>
       </c>
       <c r="B255" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C255" t="s">
         <v>11</v>
@@ -9248,18 +9251,18 @@
         <v>15</v>
       </c>
       <c r="I255">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J255">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="256" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A256" s="1">
-        <v>613524104046</v>
+        <v>613524104047</v>
       </c>
       <c r="B256" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C256" t="s">
         <v>11</v>
@@ -9280,18 +9283,18 @@
         <v>77</v>
       </c>
       <c r="I256">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="J256">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="257" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A257" s="1">
-        <v>613524104046</v>
+      <c r="A257" s="1" t="s">
+        <v>86</v>
       </c>
       <c r="B257" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C257" t="s">
         <v>11</v>
@@ -9312,18 +9315,18 @@
         <v>83</v>
       </c>
       <c r="I257">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J257">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="258" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A258" s="1">
-        <v>613524104046</v>
+        <v>613524104047</v>
       </c>
       <c r="B258" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C258" t="s">
         <v>11</v>
@@ -9344,18 +9347,18 @@
         <v>75</v>
       </c>
       <c r="I258">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J258">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="259" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A259" s="1">
-        <v>613524104046</v>
+        <v>613524104047</v>
       </c>
       <c r="B259" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C259" t="s">
         <v>11</v>
@@ -9376,18 +9379,18 @@
         <v>81</v>
       </c>
       <c r="I259">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J259">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="260" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A260" s="1">
-        <v>613524104046</v>
+        <v>613524104047</v>
       </c>
       <c r="B260" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C260" t="s">
         <v>11</v>
@@ -9408,18 +9411,18 @@
         <v>79</v>
       </c>
       <c r="I260">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J260">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="261" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A261" s="1">
-        <v>613524104047</v>
+        <v>613524104048</v>
       </c>
       <c r="B261" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C261" t="s">
         <v>11</v>
@@ -9440,18 +9443,18 @@
         <v>73</v>
       </c>
       <c r="I261">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J261">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="262" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A262" s="1">
-        <v>613524104047</v>
+        <v>613524104048</v>
       </c>
       <c r="B262" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C262" t="s">
         <v>11</v>
@@ -9472,18 +9475,18 @@
         <v>15</v>
       </c>
       <c r="I262">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J262">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="263" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A263" s="1">
-        <v>613524104047</v>
+        <v>613524104048</v>
       </c>
       <c r="B263" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C263" t="s">
         <v>11</v>
@@ -9504,18 +9507,18 @@
         <v>77</v>
       </c>
       <c r="I263">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="J263">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="264" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A264" s="1">
-        <v>613524104047</v>
+        <v>613524104048</v>
       </c>
       <c r="B264" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C264" t="s">
         <v>11</v>
@@ -9536,18 +9539,18 @@
         <v>83</v>
       </c>
       <c r="I264">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J264">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="265" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A265" s="1">
-        <v>613524104047</v>
+        <v>613524104048</v>
       </c>
       <c r="B265" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C265" t="s">
         <v>11</v>
@@ -9568,18 +9571,18 @@
         <v>75</v>
       </c>
       <c r="I265">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J265">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="266" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A266" s="1">
-        <v>613524104047</v>
+        <v>613524104048</v>
       </c>
       <c r="B266" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C266" t="s">
         <v>11</v>
@@ -9600,18 +9603,18 @@
         <v>81</v>
       </c>
       <c r="I266">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J266">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="267" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A267" s="1">
-        <v>613524104047</v>
+        <v>613524104048</v>
       </c>
       <c r="B267" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C267" t="s">
         <v>11</v>
@@ -9632,18 +9635,18 @@
         <v>79</v>
       </c>
       <c r="I267">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J267">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="268" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A268" s="1">
-        <v>613524104048</v>
+        <v>613524104049</v>
       </c>
       <c r="B268" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C268" t="s">
         <v>11</v>
@@ -9664,18 +9667,18 @@
         <v>73</v>
       </c>
       <c r="I268">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J268">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="269" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A269" s="1">
-        <v>613524104048</v>
+        <v>613524104049</v>
       </c>
       <c r="B269" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C269" t="s">
         <v>11</v>
@@ -9696,18 +9699,18 @@
         <v>15</v>
       </c>
       <c r="I269">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J269">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="270" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A270" s="1">
-        <v>613524104048</v>
+        <v>613524104049</v>
       </c>
       <c r="B270" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C270" t="s">
         <v>11</v>
@@ -9728,18 +9731,18 @@
         <v>77</v>
       </c>
       <c r="I270">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="J270">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="271" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A271" s="1">
-        <v>613524104048</v>
+        <v>613524104049</v>
       </c>
       <c r="B271" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C271" t="s">
         <v>11</v>
@@ -9760,18 +9763,18 @@
         <v>83</v>
       </c>
       <c r="I271">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J271">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="272" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A272" s="1">
-        <v>613524104048</v>
+        <v>613524104049</v>
       </c>
       <c r="B272" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C272" t="s">
         <v>11</v>
@@ -9792,18 +9795,18 @@
         <v>75</v>
       </c>
       <c r="I272">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J272">
-        <v>16</v>
+        <v>26</v>
       </c>
     </row>
     <row r="273" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A273" s="1">
-        <v>613524104048</v>
+        <v>613524104049</v>
       </c>
       <c r="B273" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C273" t="s">
         <v>11</v>
@@ -9824,18 +9827,18 @@
         <v>81</v>
       </c>
       <c r="I273">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J273">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="274" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A274" s="1">
-        <v>613524104048</v>
+        <v>613524104049</v>
       </c>
       <c r="B274" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C274" t="s">
         <v>11</v>
@@ -9856,18 +9859,18 @@
         <v>79</v>
       </c>
       <c r="I274">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J274">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="275" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A275" s="1">
-        <v>613524104049</v>
+        <v>613524104050</v>
       </c>
       <c r="B275" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C275" t="s">
         <v>11</v>
@@ -9888,18 +9891,18 @@
         <v>73</v>
       </c>
       <c r="I275">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J275">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="276" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A276" s="1">
-        <v>613524104049</v>
+        <v>613524104050</v>
       </c>
       <c r="B276" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C276" t="s">
         <v>11</v>
@@ -9920,18 +9923,18 @@
         <v>15</v>
       </c>
       <c r="I276">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J276">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="277" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A277" s="1">
-        <v>613524104049</v>
+        <v>613524104050</v>
       </c>
       <c r="B277" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C277" t="s">
         <v>11</v>
@@ -9952,18 +9955,18 @@
         <v>77</v>
       </c>
       <c r="I277">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="J277">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="278" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A278" s="1">
-        <v>613524104049</v>
+        <v>613524104050</v>
       </c>
       <c r="B278" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C278" t="s">
         <v>11</v>
@@ -9984,18 +9987,18 @@
         <v>83</v>
       </c>
       <c r="I278">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J278">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="279" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A279" s="1">
-        <v>613524104049</v>
+        <v>613524104050</v>
       </c>
       <c r="B279" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C279" t="s">
         <v>11</v>
@@ -10016,18 +10019,18 @@
         <v>75</v>
       </c>
       <c r="I279">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J279">
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="280" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A280" s="1">
-        <v>613524104049</v>
+        <v>613524104050</v>
       </c>
       <c r="B280" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C280" t="s">
         <v>11</v>
@@ -10048,18 +10051,18 @@
         <v>81</v>
       </c>
       <c r="I280">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J280">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="281" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A281" s="1">
-        <v>613524104049</v>
+        <v>613524104050</v>
       </c>
       <c r="B281" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C281" t="s">
         <v>11</v>
@@ -10080,18 +10083,18 @@
         <v>79</v>
       </c>
       <c r="I281">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J281">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="282" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A282" s="1">
-        <v>613524104050</v>
+        <v>613524104051</v>
       </c>
       <c r="B282" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C282" t="s">
         <v>11</v>
@@ -10112,18 +10115,18 @@
         <v>73</v>
       </c>
       <c r="I282">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J282">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="283" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A283" s="1">
-        <v>613524104050</v>
+        <v>613524104051</v>
       </c>
       <c r="B283" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C283" t="s">
         <v>11</v>
@@ -10144,18 +10147,18 @@
         <v>15</v>
       </c>
       <c r="I283">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J283">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="284" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A284" s="1">
-        <v>613524104050</v>
+        <v>613524104051</v>
       </c>
       <c r="B284" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C284" t="s">
         <v>11</v>
@@ -10176,18 +10179,18 @@
         <v>77</v>
       </c>
       <c r="I284">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="J284">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="285" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A285" s="1">
-        <v>613524104050</v>
+        <v>613524104051</v>
       </c>
       <c r="B285" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C285" t="s">
         <v>11</v>
@@ -10208,18 +10211,18 @@
         <v>83</v>
       </c>
       <c r="I285">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J285">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="286" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A286" s="1">
-        <v>613524104050</v>
+        <v>613524104051</v>
       </c>
       <c r="B286" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C286" t="s">
         <v>11</v>
@@ -10240,18 +10243,18 @@
         <v>75</v>
       </c>
       <c r="I286">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J286">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="287" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A287" s="1">
-        <v>613524104050</v>
+        <v>613524104051</v>
       </c>
       <c r="B287" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C287" t="s">
         <v>11</v>
@@ -10272,18 +10275,18 @@
         <v>81</v>
       </c>
       <c r="I287">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J287">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="288" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A288" s="1">
-        <v>613524104050</v>
+        <v>613524104051</v>
       </c>
       <c r="B288" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C288" t="s">
         <v>11</v>
@@ -10304,18 +10307,18 @@
         <v>79</v>
       </c>
       <c r="I288">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J288">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="289" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A289" s="1">
-        <v>613524104051</v>
+        <v>613524104052</v>
       </c>
       <c r="B289" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C289" t="s">
         <v>11</v>
@@ -10336,18 +10339,18 @@
         <v>73</v>
       </c>
       <c r="I289">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J289">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="290" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A290" s="1">
-        <v>613524104051</v>
+        <v>613524104052</v>
       </c>
       <c r="B290" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C290" t="s">
         <v>11</v>
@@ -10368,18 +10371,18 @@
         <v>15</v>
       </c>
       <c r="I290">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J290">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="291" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A291" s="1">
-        <v>613524104051</v>
+        <v>613524104052</v>
       </c>
       <c r="B291" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C291" t="s">
         <v>11</v>
@@ -10400,18 +10403,18 @@
         <v>77</v>
       </c>
       <c r="I291">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="J291">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="292" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A292" s="1">
-        <v>613524104051</v>
+        <v>613524104052</v>
       </c>
       <c r="B292" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C292" t="s">
         <v>11</v>
@@ -10432,18 +10435,18 @@
         <v>83</v>
       </c>
       <c r="I292">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J292">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="293" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A293" s="1">
-        <v>613524104051</v>
+        <v>613524104052</v>
       </c>
       <c r="B293" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C293" t="s">
         <v>11</v>
@@ -10464,18 +10467,18 @@
         <v>75</v>
       </c>
       <c r="I293">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J293">
-        <v>12</v>
+        <v>25</v>
       </c>
     </row>
     <row r="294" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A294" s="1">
-        <v>613524104051</v>
+        <v>613524104052</v>
       </c>
       <c r="B294" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C294" t="s">
         <v>11</v>
@@ -10496,18 +10499,18 @@
         <v>81</v>
       </c>
       <c r="I294">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J294">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="295" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A295" s="1">
-        <v>613524104051</v>
+        <v>613524104052</v>
       </c>
       <c r="B295" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C295" t="s">
         <v>11</v>
@@ -10528,18 +10531,18 @@
         <v>79</v>
       </c>
       <c r="I295">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J295">
-        <v>11</v>
+        <v>20</v>
       </c>
     </row>
     <row r="296" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A296" s="1">
-        <v>613524104052</v>
+        <v>613524104055</v>
       </c>
       <c r="B296" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C296" t="s">
         <v>11</v>
@@ -10560,18 +10563,18 @@
         <v>73</v>
       </c>
       <c r="I296">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J296">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="297" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A297" s="1">
-        <v>613524104052</v>
+        <v>613524104055</v>
       </c>
       <c r="B297" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C297" t="s">
         <v>11</v>
@@ -10592,18 +10595,18 @@
         <v>15</v>
       </c>
       <c r="I297">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J297">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="298" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A298" s="1">
-        <v>613524104052</v>
+        <v>613524104055</v>
       </c>
       <c r="B298" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C298" t="s">
         <v>11</v>
@@ -10624,18 +10627,18 @@
         <v>77</v>
       </c>
       <c r="I298">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="J298">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="299" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A299" s="1">
-        <v>613524104052</v>
+        <v>613524104055</v>
       </c>
       <c r="B299" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C299" t="s">
         <v>11</v>
@@ -10656,18 +10659,18 @@
         <v>83</v>
       </c>
       <c r="I299">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J299">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="300" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A300" s="1">
-        <v>613524104052</v>
+        <v>613524104055</v>
       </c>
       <c r="B300" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C300" t="s">
         <v>11</v>
@@ -10688,18 +10691,18 @@
         <v>75</v>
       </c>
       <c r="I300">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J300">
-        <v>16</v>
+        <v>26</v>
       </c>
     </row>
     <row r="301" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A301" s="1">
-        <v>613524104052</v>
+        <v>613524104055</v>
       </c>
       <c r="B301" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C301" t="s">
         <v>11</v>
@@ -10720,18 +10723,18 @@
         <v>81</v>
       </c>
       <c r="I301">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J301">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="302" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A302" s="1">
-        <v>613524104052</v>
+        <v>613524104055</v>
       </c>
       <c r="B302" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C302" t="s">
         <v>11</v>
@@ -10752,18 +10755,18 @@
         <v>79</v>
       </c>
       <c r="I302">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J302">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="303" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A303" s="1">
-        <v>613524104055</v>
+        <v>613524104056</v>
       </c>
       <c r="B303" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C303" t="s">
         <v>11</v>
@@ -10784,18 +10787,18 @@
         <v>73</v>
       </c>
       <c r="I303">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J303">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="304" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A304" s="1">
-        <v>613524104055</v>
+        <v>613524104056</v>
       </c>
       <c r="B304" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C304" t="s">
         <v>11</v>
@@ -10816,18 +10819,18 @@
         <v>15</v>
       </c>
       <c r="I304">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J304">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="305" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A305" s="1">
-        <v>613524104055</v>
+        <v>613524104056</v>
       </c>
       <c r="B305" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C305" t="s">
         <v>11</v>
@@ -10848,18 +10851,18 @@
         <v>77</v>
       </c>
       <c r="I305">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="J305">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="306" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A306" s="1">
-        <v>613524104055</v>
+        <v>613524104056</v>
       </c>
       <c r="B306" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C306" t="s">
         <v>11</v>
@@ -10880,18 +10883,18 @@
         <v>83</v>
       </c>
       <c r="I306">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J306">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="307" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A307" s="1">
-        <v>613524104055</v>
+        <v>613524104056</v>
       </c>
       <c r="B307" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C307" t="s">
         <v>11</v>
@@ -10912,18 +10915,18 @@
         <v>75</v>
       </c>
       <c r="I307">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J307">
-        <v>17</v>
+        <v>26</v>
       </c>
     </row>
     <row r="308" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A308" s="1">
-        <v>613524104055</v>
+        <v>613524104056</v>
       </c>
       <c r="B308" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C308" t="s">
         <v>11</v>
@@ -10944,18 +10947,18 @@
         <v>81</v>
       </c>
       <c r="I308">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J308">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="309" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A309" s="1">
-        <v>613524104055</v>
+        <v>613524104056</v>
       </c>
       <c r="B309" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C309" t="s">
         <v>11</v>
@@ -10976,18 +10979,18 @@
         <v>79</v>
       </c>
       <c r="I309">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J309">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="310" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A310" s="1">
-        <v>613524104056</v>
+        <v>613524104057</v>
       </c>
       <c r="B310" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C310" t="s">
         <v>11</v>
@@ -11008,18 +11011,18 @@
         <v>73</v>
       </c>
       <c r="I310">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J310">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="311" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A311" s="1">
-        <v>613524104056</v>
+        <v>613524104057</v>
       </c>
       <c r="B311" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C311" t="s">
         <v>11</v>
@@ -11040,18 +11043,18 @@
         <v>15</v>
       </c>
       <c r="I311">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J311">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="312" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A312" s="1">
-        <v>613524104056</v>
+        <v>613524104057</v>
       </c>
       <c r="B312" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C312" t="s">
         <v>11</v>
@@ -11072,18 +11075,18 @@
         <v>77</v>
       </c>
       <c r="I312">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="J312">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="313" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A313" s="1">
-        <v>613524104056</v>
+        <v>613524104057</v>
       </c>
       <c r="B313" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C313" t="s">
         <v>11</v>
@@ -11104,18 +11107,18 @@
         <v>83</v>
       </c>
       <c r="I313">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J313">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="314" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A314" s="1">
-        <v>613524104056</v>
+        <v>613524104057</v>
       </c>
       <c r="B314" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C314" t="s">
         <v>11</v>
@@ -11136,18 +11139,18 @@
         <v>75</v>
       </c>
       <c r="I314">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J314">
-        <v>17</v>
+        <v>26</v>
       </c>
     </row>
     <row r="315" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A315" s="1">
-        <v>613524104056</v>
+        <v>613524104057</v>
       </c>
       <c r="B315" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C315" t="s">
         <v>11</v>
@@ -11168,18 +11171,18 @@
         <v>81</v>
       </c>
       <c r="I315">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J315">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="316" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A316" s="1">
-        <v>613524104056</v>
+        <v>613524104057</v>
       </c>
       <c r="B316" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C316" t="s">
         <v>11</v>
@@ -11200,18 +11203,18 @@
         <v>79</v>
       </c>
       <c r="I316">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J316">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="317" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A317" s="1">
-        <v>613524104057</v>
+        <v>613524104058</v>
       </c>
       <c r="B317" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C317" t="s">
         <v>11</v>
@@ -11232,18 +11235,18 @@
         <v>73</v>
       </c>
       <c r="I317">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J317">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="318" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A318" s="1">
-        <v>613524104057</v>
+        <v>613524104058</v>
       </c>
       <c r="B318" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C318" t="s">
         <v>11</v>
@@ -11264,18 +11267,18 @@
         <v>15</v>
       </c>
       <c r="I318">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J318">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="319" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A319" s="1">
-        <v>613524104057</v>
+        <v>613524104058</v>
       </c>
       <c r="B319" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C319" t="s">
         <v>11</v>
@@ -11296,18 +11299,18 @@
         <v>77</v>
       </c>
       <c r="I319">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="J319">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="320" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A320" s="1">
-        <v>613524104057</v>
+        <v>613524104058</v>
       </c>
       <c r="B320" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C320" t="s">
         <v>11</v>
@@ -11328,18 +11331,18 @@
         <v>83</v>
       </c>
       <c r="I320">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J320">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="321" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A321" s="1">
-        <v>613524104057</v>
+        <v>613524104058</v>
       </c>
       <c r="B321" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C321" t="s">
         <v>11</v>
@@ -11360,7 +11363,7 @@
         <v>75</v>
       </c>
       <c r="I321">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J321">
         <v>17</v>
@@ -11368,10 +11371,10 @@
     </row>
     <row r="322" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A322" s="1">
-        <v>613524104057</v>
+        <v>613524104058</v>
       </c>
       <c r="B322" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C322" t="s">
         <v>11</v>
@@ -11392,18 +11395,18 @@
         <v>81</v>
       </c>
       <c r="I322">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J322">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="323" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A323" s="1">
-        <v>613524104057</v>
+        <v>613524104058</v>
       </c>
       <c r="B323" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C323" t="s">
         <v>11</v>
@@ -11424,18 +11427,18 @@
         <v>79</v>
       </c>
       <c r="I323">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J323">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="324" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A324" s="1">
-        <v>613524104058</v>
+        <v>613524104301</v>
       </c>
       <c r="B324" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C324" t="s">
         <v>11</v>
@@ -11456,18 +11459,18 @@
         <v>73</v>
       </c>
       <c r="I324">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J324">
-        <v>6</v>
+        <v>17</v>
       </c>
     </row>
     <row r="325" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A325" s="1">
-        <v>613524104058</v>
+        <v>613524104301</v>
       </c>
       <c r="B325" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C325" t="s">
         <v>11</v>
@@ -11488,18 +11491,18 @@
         <v>15</v>
       </c>
       <c r="I325">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J325">
-        <v>6</v>
+        <v>17</v>
       </c>
     </row>
     <row r="326" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A326" s="1">
-        <v>613524104058</v>
+        <v>613524104301</v>
       </c>
       <c r="B326" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C326" t="s">
         <v>11</v>
@@ -11520,18 +11523,18 @@
         <v>77</v>
       </c>
       <c r="I326">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="J326">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="327" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A327" s="1">
-        <v>613524104058</v>
+        <v>613524104301</v>
       </c>
       <c r="B327" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C327" t="s">
         <v>11</v>
@@ -11552,18 +11555,18 @@
         <v>83</v>
       </c>
       <c r="I327">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J327">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="328" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A328" s="1">
-        <v>613524104058</v>
+        <v>613524104301</v>
       </c>
       <c r="B328" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C328" t="s">
         <v>11</v>
@@ -11584,18 +11587,18 @@
         <v>75</v>
       </c>
       <c r="I328">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J328">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row r="329" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A329" s="1">
-        <v>613524104058</v>
+        <v>613524104301</v>
       </c>
       <c r="B329" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C329" t="s">
         <v>11</v>
@@ -11616,18 +11619,18 @@
         <v>81</v>
       </c>
       <c r="I329">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J329">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="330" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A330" s="1">
-        <v>613524104058</v>
+        <v>613524104301</v>
       </c>
       <c r="B330" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C330" t="s">
         <v>11</v>
@@ -11648,18 +11651,18 @@
         <v>79</v>
       </c>
       <c r="I330">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J330">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="331" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A331" s="1">
-        <v>613524104301</v>
+        <v>613524104302</v>
       </c>
       <c r="B331" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C331" t="s">
         <v>11</v>
@@ -11680,18 +11683,18 @@
         <v>73</v>
       </c>
       <c r="I331">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J331">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="332" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A332" s="1">
-        <v>613524104301</v>
+        <v>613524104302</v>
       </c>
       <c r="B332" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C332" t="s">
         <v>11</v>
@@ -11712,18 +11715,18 @@
         <v>15</v>
       </c>
       <c r="I332">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J332">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="333" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A333" s="1">
-        <v>613524104301</v>
+        <v>613524104302</v>
       </c>
       <c r="B333" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C333" t="s">
         <v>11</v>
@@ -11744,18 +11747,18 @@
         <v>77</v>
       </c>
       <c r="I333">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="J333">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="334" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A334" s="1">
-        <v>613524104301</v>
+        <v>613524104302</v>
       </c>
       <c r="B334" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C334" t="s">
         <v>11</v>
@@ -11776,18 +11779,18 @@
         <v>83</v>
       </c>
       <c r="I334">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J334">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="335" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A335" s="1">
-        <v>613524104301</v>
+        <v>613524104302</v>
       </c>
       <c r="B335" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C335" t="s">
         <v>11</v>
@@ -11808,18 +11811,18 @@
         <v>75</v>
       </c>
       <c r="I335">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J335">
-        <v>17</v>
+        <v>26</v>
       </c>
     </row>
     <row r="336" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A336" s="1">
-        <v>613524104301</v>
+        <v>613524104302</v>
       </c>
       <c r="B336" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C336" t="s">
         <v>11</v>
@@ -11840,18 +11843,18 @@
         <v>81</v>
       </c>
       <c r="I336">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J336">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="337" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A337" s="1">
-        <v>613524104301</v>
+        <v>613524104302</v>
       </c>
       <c r="B337" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C337" t="s">
         <v>11</v>
@@ -11872,18 +11875,18 @@
         <v>79</v>
       </c>
       <c r="I337">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J337">
-        <v>11</v>
+        <v>18</v>
       </c>
     </row>
     <row r="338" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A338" s="1">
-        <v>613524104302</v>
+        <v>613524104303</v>
       </c>
       <c r="B338" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C338" t="s">
         <v>11</v>
@@ -11904,18 +11907,18 @@
         <v>73</v>
       </c>
       <c r="I338">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J338">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="339" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A339" s="1">
-        <v>613524104302</v>
+        <v>613524104303</v>
       </c>
       <c r="B339" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C339" t="s">
         <v>11</v>
@@ -11936,18 +11939,18 @@
         <v>15</v>
       </c>
       <c r="I339">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J339">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="340" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A340" s="1">
-        <v>613524104302</v>
+        <v>613524104303</v>
       </c>
       <c r="B340" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C340" t="s">
         <v>11</v>
@@ -11968,18 +11971,18 @@
         <v>77</v>
       </c>
       <c r="I340">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="J340">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="341" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A341" s="1">
-        <v>613524104302</v>
+        <v>613524104303</v>
       </c>
       <c r="B341" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C341" t="s">
         <v>11</v>
@@ -12000,18 +12003,18 @@
         <v>83</v>
       </c>
       <c r="I341">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J341">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="342" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A342" s="1">
-        <v>613524104302</v>
+        <v>613524104303</v>
       </c>
       <c r="B342" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C342" t="s">
         <v>11</v>
@@ -12032,18 +12035,18 @@
         <v>75</v>
       </c>
       <c r="I342">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J342">
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="343" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A343" s="1">
-        <v>613524104302</v>
+        <v>613524104303</v>
       </c>
       <c r="B343" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C343" t="s">
         <v>11</v>
@@ -12064,18 +12067,18 @@
         <v>81</v>
       </c>
       <c r="I343">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J343">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="344" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A344" s="1">
-        <v>613524104302</v>
+        <v>613524104303</v>
       </c>
       <c r="B344" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C344" t="s">
         <v>11</v>
@@ -12096,18 +12099,18 @@
         <v>79</v>
       </c>
       <c r="I344">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J344">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="345" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A345" s="1">
-        <v>613524104303</v>
+        <v>613524104701</v>
       </c>
       <c r="B345" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C345" t="s">
         <v>11</v>
@@ -12128,18 +12131,18 @@
         <v>73</v>
       </c>
       <c r="I345">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J345">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="346" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A346" s="1">
-        <v>613524104303</v>
+        <v>613524104701</v>
       </c>
       <c r="B346" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C346" t="s">
         <v>11</v>
@@ -12160,18 +12163,18 @@
         <v>15</v>
       </c>
       <c r="I346">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J346">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="347" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A347" s="1">
-        <v>613524104303</v>
+        <v>613524104701</v>
       </c>
       <c r="B347" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C347" t="s">
         <v>11</v>
@@ -12192,18 +12195,18 @@
         <v>77</v>
       </c>
       <c r="I347">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="J347">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="348" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A348" s="1">
-        <v>613524104303</v>
+        <v>613524104701</v>
       </c>
       <c r="B348" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C348" t="s">
         <v>11</v>
@@ -12224,18 +12227,18 @@
         <v>83</v>
       </c>
       <c r="I348">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J348">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="349" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A349" s="1">
-        <v>613524104303</v>
+        <v>613524104701</v>
       </c>
       <c r="B349" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C349" t="s">
         <v>11</v>
@@ -12256,18 +12259,18 @@
         <v>75</v>
       </c>
       <c r="I349">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J349">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="350" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A350" s="1">
-        <v>613524104303</v>
+        <v>613524104701</v>
       </c>
       <c r="B350" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C350" t="s">
         <v>11</v>
@@ -12288,18 +12291,18 @@
         <v>81</v>
       </c>
       <c r="I350">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J350">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="351" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A351" s="1">
-        <v>613524104303</v>
+        <v>613524104701</v>
       </c>
       <c r="B351" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C351" t="s">
         <v>11</v>
@@ -12320,18 +12323,18 @@
         <v>79</v>
       </c>
       <c r="I351">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J351">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="352" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A352" s="1">
-        <v>613524104701</v>
+        <v>613524104702</v>
       </c>
       <c r="B352" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C352" t="s">
         <v>11</v>
@@ -12352,18 +12355,18 @@
         <v>73</v>
       </c>
       <c r="I352">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J352">
-        <v>6</v>
+        <v>17</v>
       </c>
     </row>
     <row r="353" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A353" s="1">
-        <v>613524104701</v>
+        <v>613524104702</v>
       </c>
       <c r="B353" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C353" t="s">
         <v>11</v>
@@ -12384,18 +12387,18 @@
         <v>15</v>
       </c>
       <c r="I353">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J353">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="354" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A354" s="1">
-        <v>613524104701</v>
+        <v>613524104702</v>
       </c>
       <c r="B354" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C354" t="s">
         <v>11</v>
@@ -12416,18 +12419,18 @@
         <v>77</v>
       </c>
       <c r="I354">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="J354">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="355" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A355" s="1">
-        <v>613524104701</v>
+        <v>613524104702</v>
       </c>
       <c r="B355" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C355" t="s">
         <v>11</v>
@@ -12448,18 +12451,18 @@
         <v>83</v>
       </c>
       <c r="I355">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J355">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="356" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A356" s="1">
-        <v>613524104701</v>
+        <v>613524104702</v>
       </c>
       <c r="B356" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C356" t="s">
         <v>11</v>
@@ -12480,18 +12483,18 @@
         <v>75</v>
       </c>
       <c r="I356">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J356">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="357" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A357" s="1">
-        <v>613524104701</v>
+        <v>613524104702</v>
       </c>
       <c r="B357" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C357" t="s">
         <v>11</v>
@@ -12512,18 +12515,18 @@
         <v>81</v>
       </c>
       <c r="I357">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J357">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="358" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A358" s="1">
-        <v>613524104701</v>
+        <v>613524104702</v>
       </c>
       <c r="B358" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C358" t="s">
         <v>11</v>
@@ -12544,18 +12547,18 @@
         <v>79</v>
       </c>
       <c r="I358">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J358">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="359" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A359" s="1">
-        <v>613524104702</v>
+        <v>613524104703</v>
       </c>
       <c r="B359" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C359" t="s">
         <v>11</v>
@@ -12576,18 +12579,18 @@
         <v>73</v>
       </c>
       <c r="I359">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J359">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="360" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A360" s="1">
-        <v>613524104702</v>
+        <v>613524104703</v>
       </c>
       <c r="B360" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C360" t="s">
         <v>11</v>
@@ -12608,18 +12611,18 @@
         <v>15</v>
       </c>
       <c r="I360">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J360">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="361" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A361" s="1">
-        <v>613524104702</v>
+        <v>613524104703</v>
       </c>
       <c r="B361" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C361" t="s">
         <v>11</v>
@@ -12640,18 +12643,18 @@
         <v>77</v>
       </c>
       <c r="I361">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="J361">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="362" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A362" s="1">
-        <v>613524104702</v>
+        <v>613524104703</v>
       </c>
       <c r="B362" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C362" t="s">
         <v>11</v>
@@ -12672,18 +12675,18 @@
         <v>83</v>
       </c>
       <c r="I362">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J362">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="363" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A363" s="1">
-        <v>613524104702</v>
+        <v>613524104703</v>
       </c>
       <c r="B363" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C363" t="s">
         <v>11</v>
@@ -12704,18 +12707,18 @@
         <v>75</v>
       </c>
       <c r="I363">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J363">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row r="364" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A364" s="1">
-        <v>613524104702</v>
+        <v>613524104703</v>
       </c>
       <c r="B364" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C364" t="s">
         <v>11</v>
@@ -12736,18 +12739,18 @@
         <v>81</v>
       </c>
       <c r="I364">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J364">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="365" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A365" s="1">
-        <v>613524104702</v>
+        <v>613524104703</v>
       </c>
       <c r="B365" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C365" t="s">
         <v>11</v>
@@ -12768,18 +12771,18 @@
         <v>79</v>
       </c>
       <c r="I365">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J365">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="366" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A366" s="1">
-        <v>613524104703</v>
+        <v>613524104704</v>
       </c>
       <c r="B366" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C366" t="s">
         <v>11</v>
@@ -12800,18 +12803,18 @@
         <v>73</v>
       </c>
       <c r="I366">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J366">
-        <v>6</v>
+        <v>17</v>
       </c>
     </row>
     <row r="367" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A367" s="1">
-        <v>613524104703</v>
+        <v>613524104704</v>
       </c>
       <c r="B367" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C367" t="s">
         <v>11</v>
@@ -12832,18 +12835,18 @@
         <v>15</v>
       </c>
       <c r="I367">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J367">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="368" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A368" s="1">
-        <v>613524104703</v>
+        <v>613524104704</v>
       </c>
       <c r="B368" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C368" t="s">
         <v>11</v>
@@ -12864,18 +12867,18 @@
         <v>77</v>
       </c>
       <c r="I368">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="J368">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="369" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A369" s="1">
-        <v>613524104703</v>
+        <v>613524104704</v>
       </c>
       <c r="B369" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C369" t="s">
         <v>11</v>
@@ -12896,18 +12899,18 @@
         <v>83</v>
       </c>
       <c r="I369">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J369">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="370" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A370" s="1">
-        <v>613524104703</v>
+        <v>613524104704</v>
       </c>
       <c r="B370" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C370" t="s">
         <v>11</v>
@@ -12928,18 +12931,18 @@
         <v>75</v>
       </c>
       <c r="I370">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J370">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="371" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A371" s="1">
-        <v>613524104703</v>
+        <v>613524104704</v>
       </c>
       <c r="B371" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C371" t="s">
         <v>11</v>
@@ -12960,18 +12963,18 @@
         <v>81</v>
       </c>
       <c r="I371">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J371">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="372" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A372" s="1">
-        <v>613524104703</v>
+        <v>613524104704</v>
       </c>
       <c r="B372" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C372" t="s">
         <v>11</v>
@@ -12992,18 +12995,18 @@
         <v>79</v>
       </c>
       <c r="I372">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J372">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="373" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A373" s="1">
-        <v>613524104704</v>
+        <v>613524104705</v>
       </c>
       <c r="B373" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C373" t="s">
         <v>11</v>
@@ -13024,18 +13027,18 @@
         <v>73</v>
       </c>
       <c r="I373">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J373">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="374" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A374" s="1">
-        <v>613524104704</v>
+        <v>613524104705</v>
       </c>
       <c r="B374" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C374" t="s">
         <v>11</v>
@@ -13056,18 +13059,18 @@
         <v>15</v>
       </c>
       <c r="I374">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J374">
-        <v>6</v>
+        <v>18</v>
       </c>
     </row>
     <row r="375" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A375" s="1">
-        <v>613524104704</v>
+        <v>613524104705</v>
       </c>
       <c r="B375" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C375" t="s">
         <v>11</v>
@@ -13088,18 +13091,18 @@
         <v>77</v>
       </c>
       <c r="I375">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="J375">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="376" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A376" s="1">
-        <v>613524104704</v>
+        <v>613524104705</v>
       </c>
       <c r="B376" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C376" t="s">
         <v>11</v>
@@ -13120,18 +13123,18 @@
         <v>83</v>
       </c>
       <c r="I376">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J376">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="377" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A377" s="1">
-        <v>613524104704</v>
+        <v>613524104705</v>
       </c>
       <c r="B377" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C377" t="s">
         <v>11</v>
@@ -13152,18 +13155,18 @@
         <v>75</v>
       </c>
       <c r="I377">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J377">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="378" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A378" s="1">
-        <v>613524104704</v>
+        <v>613524104705</v>
       </c>
       <c r="B378" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C378" t="s">
         <v>11</v>
@@ -13184,18 +13187,18 @@
         <v>81</v>
       </c>
       <c r="I378">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J378">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="379" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A379" s="1">
-        <v>613524104704</v>
+        <v>613524104705</v>
       </c>
       <c r="B379" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C379" t="s">
         <v>11</v>
@@ -13216,18 +13219,18 @@
         <v>79</v>
       </c>
       <c r="I379">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J379">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="380" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A380" s="1">
-        <v>613524104705</v>
+        <v>613524104706</v>
       </c>
       <c r="B380" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C380" t="s">
         <v>11</v>
@@ -13248,18 +13251,18 @@
         <v>73</v>
       </c>
       <c r="I380">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J380">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="381" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A381" s="1">
-        <v>613524104705</v>
+        <v>613524104706</v>
       </c>
       <c r="B381" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C381" t="s">
         <v>11</v>
@@ -13280,18 +13283,18 @@
         <v>15</v>
       </c>
       <c r="I381">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J381">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="382" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A382" s="1">
-        <v>613524104705</v>
+        <v>613524104706</v>
       </c>
       <c r="B382" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C382" t="s">
         <v>11</v>
@@ -13312,18 +13315,18 @@
         <v>77</v>
       </c>
       <c r="I382">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="J382">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="383" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A383" s="1">
-        <v>613524104705</v>
+        <v>613524104706</v>
       </c>
       <c r="B383" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C383" t="s">
         <v>11</v>
@@ -13344,18 +13347,18 @@
         <v>83</v>
       </c>
       <c r="I383">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J383">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="384" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A384" s="1">
-        <v>613524104705</v>
+        <v>613524104706</v>
       </c>
       <c r="B384" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C384" t="s">
         <v>11</v>
@@ -13376,18 +13379,18 @@
         <v>75</v>
       </c>
       <c r="I384">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J384">
-        <v>13</v>
+        <v>27</v>
       </c>
     </row>
     <row r="385" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A385" s="1">
-        <v>613524104705</v>
+        <v>613524104706</v>
       </c>
       <c r="B385" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C385" t="s">
         <v>11</v>
@@ -13408,18 +13411,18 @@
         <v>81</v>
       </c>
       <c r="I385">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J385">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="386" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A386" s="1">
-        <v>613524104705</v>
+        <v>613524104706</v>
       </c>
       <c r="B386" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C386" t="s">
         <v>11</v>
@@ -13440,18 +13443,18 @@
         <v>79</v>
       </c>
       <c r="I386">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J386">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="387" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A387" s="1">
-        <v>613524104706</v>
+        <v>613524104707</v>
       </c>
       <c r="B387" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C387" t="s">
         <v>11</v>
@@ -13472,18 +13475,18 @@
         <v>73</v>
       </c>
       <c r="I387">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J387">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="388" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A388" s="1">
-        <v>613524104706</v>
+        <v>613524104707</v>
       </c>
       <c r="B388" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C388" t="s">
         <v>11</v>
@@ -13504,18 +13507,18 @@
         <v>15</v>
       </c>
       <c r="I388">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J388">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="389" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A389" s="1">
-        <v>613524104706</v>
+        <v>613524104707</v>
       </c>
       <c r="B389" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C389" t="s">
         <v>11</v>
@@ -13536,18 +13539,18 @@
         <v>77</v>
       </c>
       <c r="I389">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="J389">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="390" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A390" s="1">
-        <v>613524104706</v>
+        <v>613524104707</v>
       </c>
       <c r="B390" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C390" t="s">
         <v>11</v>
@@ -13568,18 +13571,18 @@
         <v>83</v>
       </c>
       <c r="I390">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J390">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="391" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A391" s="1">
-        <v>613524104706</v>
+        <v>613524104707</v>
       </c>
       <c r="B391" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C391" t="s">
         <v>11</v>
@@ -13600,18 +13603,18 @@
         <v>75</v>
       </c>
       <c r="I391">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J391">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="392" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A392" s="1">
-        <v>613524104706</v>
+        <v>613524104707</v>
       </c>
       <c r="B392" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C392" t="s">
         <v>11</v>
@@ -13632,18 +13635,18 @@
         <v>81</v>
       </c>
       <c r="I392">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J392">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="393" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A393" s="1">
-        <v>613524104706</v>
+        <v>613524104707</v>
       </c>
       <c r="B393" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C393" t="s">
         <v>11</v>
@@ -13664,18 +13667,18 @@
         <v>79</v>
       </c>
       <c r="I393">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J393">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="394" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A394" s="1">
-        <v>613524104707</v>
+        <v>613524104708</v>
       </c>
       <c r="B394" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C394" t="s">
         <v>11</v>
@@ -13696,18 +13699,18 @@
         <v>73</v>
       </c>
       <c r="I394">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J394">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="395" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A395" s="1">
-        <v>613524104707</v>
+        <v>613524104708</v>
       </c>
       <c r="B395" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C395" t="s">
         <v>11</v>
@@ -13728,18 +13731,18 @@
         <v>15</v>
       </c>
       <c r="I395">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J395">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="396" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A396" s="1">
-        <v>613524104707</v>
+        <v>613524104708</v>
       </c>
       <c r="B396" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C396" t="s">
         <v>11</v>
@@ -13760,18 +13763,18 @@
         <v>77</v>
       </c>
       <c r="I396">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="J396">
-        <v>6</v>
+        <v>18</v>
       </c>
     </row>
     <row r="397" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A397" s="1">
-        <v>613524104707</v>
+        <v>613524104708</v>
       </c>
       <c r="B397" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C397" t="s">
         <v>11</v>
@@ -13792,18 +13795,18 @@
         <v>83</v>
       </c>
       <c r="I397">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J397">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="398" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A398" s="1">
-        <v>613524104707</v>
+        <v>613524104708</v>
       </c>
       <c r="B398" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C398" t="s">
         <v>11</v>
@@ -13824,18 +13827,18 @@
         <v>75</v>
       </c>
       <c r="I398">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J398">
-        <v>15</v>
+        <v>27</v>
       </c>
     </row>
     <row r="399" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A399" s="1">
-        <v>613524104707</v>
+        <v>613524104708</v>
       </c>
       <c r="B399" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C399" t="s">
         <v>11</v>
@@ -13856,18 +13859,18 @@
         <v>81</v>
       </c>
       <c r="I399">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J399">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="400" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A400" s="1">
-        <v>613524104707</v>
+        <v>613524104708</v>
       </c>
       <c r="B400" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C400" t="s">
         <v>11</v>
@@ -13888,18 +13891,18 @@
         <v>79</v>
       </c>
       <c r="I400">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J400">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="401" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A401" s="1">
-        <v>613524104708</v>
+      <c r="A401" s="1" t="s">
+        <v>84</v>
       </c>
       <c r="B401" t="s">
-        <v>71</v>
+        <v>42</v>
       </c>
       <c r="C401" t="s">
         <v>11</v>
@@ -13920,18 +13923,18 @@
         <v>73</v>
       </c>
       <c r="I401">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J401">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="402" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A402" s="1">
-        <v>613524104708</v>
+      <c r="A402" s="1" t="s">
+        <v>84</v>
       </c>
       <c r="B402" t="s">
-        <v>71</v>
+        <v>42</v>
       </c>
       <c r="C402" t="s">
         <v>11</v>
@@ -13952,18 +13955,18 @@
         <v>15</v>
       </c>
       <c r="I402">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J402">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="403" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A403" s="1">
-        <v>613524104708</v>
+      <c r="A403" s="1" t="s">
+        <v>84</v>
       </c>
       <c r="B403" t="s">
-        <v>71</v>
+        <v>42</v>
       </c>
       <c r="C403" t="s">
         <v>11</v>
@@ -13984,18 +13987,18 @@
         <v>77</v>
       </c>
       <c r="I403">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="J403">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="404" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A404" s="1">
-        <v>613524104708</v>
+      <c r="A404" s="1" t="s">
+        <v>84</v>
       </c>
       <c r="B404" t="s">
-        <v>71</v>
+        <v>42</v>
       </c>
       <c r="C404" t="s">
         <v>11</v>
@@ -14016,18 +14019,18 @@
         <v>83</v>
       </c>
       <c r="I404">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J404">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="405" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A405" s="1">
-        <v>613524104708</v>
+      <c r="A405" s="1" t="s">
+        <v>84</v>
       </c>
       <c r="B405" t="s">
-        <v>71</v>
+        <v>42</v>
       </c>
       <c r="C405" t="s">
         <v>11</v>
@@ -14048,18 +14051,18 @@
         <v>75</v>
       </c>
       <c r="I405">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J405">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="406" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A406" s="1">
-        <v>613524104708</v>
+      <c r="A406" s="1" t="s">
+        <v>84</v>
       </c>
       <c r="B406" t="s">
-        <v>71</v>
+        <v>42</v>
       </c>
       <c r="C406" t="s">
         <v>11</v>
@@ -14080,18 +14083,18 @@
         <v>81</v>
       </c>
       <c r="I406">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J406">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="407" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A407" s="1">
-        <v>613524104708</v>
+      <c r="A407" s="1" t="s">
+        <v>84</v>
       </c>
       <c r="B407" t="s">
-        <v>71</v>
+        <v>42</v>
       </c>
       <c r="C407" t="s">
         <v>11</v>
@@ -14112,10 +14115,10 @@
         <v>79</v>
       </c>
       <c r="I407">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J407">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -14125,7 +14128,7 @@
     </sortState>
   </autoFilter>
   <sortState ref="A2:J407">
-    <sortCondition ref="H1"/>
+    <sortCondition ref="A149"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
